--- a/notebooks/XGBoost/predictions_afr_2025.xlsx
+++ b/notebooks/XGBoost/predictions_afr_2025.xlsx
@@ -460,10 +460,10 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>1.337920427322388</v>
+        <v>1.333839774131775</v>
       </c>
       <c r="D2" t="n">
-        <v>1.331998109817505</v>
+        <v>1.332483649253845</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>1.496572375297546</v>
+        <v>1.502897381782532</v>
       </c>
       <c r="D3" t="n">
-        <v>1.441084027290344</v>
+        <v>1.431456446647644</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +492,10 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>1.505865454673767</v>
+        <v>1.504938244819641</v>
       </c>
       <c r="D4" t="n">
-        <v>1.428277850151062</v>
+        <v>1.413058638572693</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +508,10 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>1.650961399078369</v>
+        <v>1.655352473258972</v>
       </c>
       <c r="D5" t="n">
-        <v>1.534860849380493</v>
+        <v>1.527954816818237</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>1.141619086265564</v>
+        <v>1.140672922134399</v>
       </c>
       <c r="D6" t="n">
-        <v>1.246714472770691</v>
+        <v>1.246144413948059</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>1.210875272750854</v>
+        <v>1.208008527755737</v>
       </c>
       <c r="D7" t="n">
-        <v>1.253820061683655</v>
+        <v>1.258081793785095</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +556,10 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>1.131332993507385</v>
+        <v>1.142362356185913</v>
       </c>
       <c r="D8" t="n">
-        <v>1.239470720291138</v>
+        <v>1.237136721611023</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +572,10 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>1.171207904815674</v>
+        <v>1.149627685546875</v>
       </c>
       <c r="D9" t="n">
-        <v>1.251896977424622</v>
+        <v>1.249036908149719</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +588,10 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>1.416334271430969</v>
+        <v>1.415530920028687</v>
       </c>
       <c r="D10" t="n">
-        <v>1.383431792259216</v>
+        <v>1.374614477157593</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>1.219371795654297</v>
+        <v>1.220258593559265</v>
       </c>
       <c r="D11" t="n">
-        <v>1.270521283149719</v>
+        <v>1.266632318496704</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +620,10 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>1.609597325325012</v>
+        <v>1.605180501937866</v>
       </c>
       <c r="D12" t="n">
-        <v>1.514526605606079</v>
+        <v>1.501436829566956</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +636,10 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>1.602985858917236</v>
+        <v>1.61126708984375</v>
       </c>
       <c r="D13" t="n">
-        <v>1.491344332695007</v>
+        <v>1.498475432395935</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>1.367660284042358</v>
+        <v>1.369040369987488</v>
       </c>
       <c r="D14" t="n">
-        <v>1.353049635887146</v>
+        <v>1.368060946464539</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +668,10 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>1.688226342201233</v>
+        <v>1.686344385147095</v>
       </c>
       <c r="D15" t="n">
-        <v>1.53930139541626</v>
+        <v>1.533150196075439</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +684,10 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>1.536739468574524</v>
+        <v>1.539897441864014</v>
       </c>
       <c r="D16" t="n">
-        <v>1.442812323570251</v>
+        <v>1.439299583435059</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +700,10 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>1.22214674949646</v>
+        <v>1.222097277641296</v>
       </c>
       <c r="D17" t="n">
-        <v>1.271775484085083</v>
+        <v>1.273413062095642</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +716,10 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>1.339912414550781</v>
+        <v>1.342038869857788</v>
       </c>
       <c r="D18" t="n">
-        <v>1.322155952453613</v>
+        <v>1.323188185691833</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>1.665318131446838</v>
+        <v>1.660814642906189</v>
       </c>
       <c r="D19" t="n">
-        <v>1.536938071250916</v>
+        <v>1.530423879623413</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +748,10 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>1.328302979469299</v>
+        <v>1.337565064430237</v>
       </c>
       <c r="D20" t="n">
-        <v>1.329525589942932</v>
+        <v>1.329493880271912</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +764,10 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>1.263764500617981</v>
+        <v>1.259890913963318</v>
       </c>
       <c r="D21" t="n">
-        <v>1.316936016082764</v>
+        <v>1.253034830093384</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +780,10 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>1.526806235313416</v>
+        <v>1.501935958862305</v>
       </c>
       <c r="D22" t="n">
-        <v>1.422048211097717</v>
+        <v>1.418921709060669</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +796,10 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>1.559346079826355</v>
+        <v>1.568055868148804</v>
       </c>
       <c r="D23" t="n">
-        <v>1.462913990020752</v>
+        <v>1.460103869438171</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +812,10 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>1.535563826560974</v>
+        <v>1.537211894989014</v>
       </c>
       <c r="D24" t="n">
-        <v>1.421826362609863</v>
+        <v>1.411762595176697</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +828,10 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>1.440383791923523</v>
+        <v>1.432950973510742</v>
       </c>
       <c r="D25" t="n">
-        <v>1.416849493980408</v>
+        <v>1.417754173278809</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +844,10 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>1.691486954689026</v>
+        <v>1.690935492515564</v>
       </c>
       <c r="D26" t="n">
-        <v>1.546326398849487</v>
+        <v>1.516912341117859</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +860,10 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>1.282421827316284</v>
+        <v>1.297560811042786</v>
       </c>
       <c r="D27" t="n">
-        <v>1.292780756950378</v>
+        <v>1.303098559379578</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +876,10 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>1.043367624282837</v>
+        <v>1.02957284450531</v>
       </c>
       <c r="D28" t="n">
-        <v>1.131433725357056</v>
+        <v>1.101929783821106</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +892,10 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>1.190237760543823</v>
+        <v>1.200989484786987</v>
       </c>
       <c r="D29" t="n">
-        <v>1.242622256278992</v>
+        <v>1.245800375938416</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +908,10 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>1.414074182510376</v>
+        <v>1.414622187614441</v>
       </c>
       <c r="D30" t="n">
-        <v>1.410825252532959</v>
+        <v>1.392966151237488</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +924,10 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>1.313364624977112</v>
+        <v>1.321791768074036</v>
       </c>
       <c r="D31" t="n">
-        <v>1.305166721343994</v>
+        <v>1.341306686401367</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +940,10 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>1.468117952346802</v>
+        <v>1.457277655601501</v>
       </c>
       <c r="D32" t="n">
-        <v>1.42950963973999</v>
+        <v>1.425849080085754</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +956,10 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>1.895154356956482</v>
+        <v>1.895996451377869</v>
       </c>
       <c r="D33" t="n">
-        <v>1.637440085411072</v>
+        <v>1.639363288879395</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +972,10 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>1.303429484367371</v>
+        <v>1.302320599555969</v>
       </c>
       <c r="D34" t="n">
-        <v>1.324918746948242</v>
+        <v>1.323935151100159</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +988,10 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>1.310843110084534</v>
+        <v>1.334379911422729</v>
       </c>
       <c r="D35" t="n">
-        <v>1.332949042320251</v>
+        <v>1.341401100158691</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +1004,10 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>1.511179566383362</v>
+        <v>1.506269812583923</v>
       </c>
       <c r="D36" t="n">
-        <v>1.416820883750916</v>
+        <v>1.43855094909668</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +1020,10 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>1.523179531097412</v>
+        <v>1.527469396591187</v>
       </c>
       <c r="D37" t="n">
-        <v>1.427938222885132</v>
+        <v>1.430280804634094</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +1036,10 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>1.505324006080627</v>
+        <v>1.507794976234436</v>
       </c>
       <c r="D38" t="n">
-        <v>1.410745024681091</v>
+        <v>1.412416815757751</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +1052,10 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>1.205562710762024</v>
+        <v>1.206899523735046</v>
       </c>
       <c r="D39" t="n">
-        <v>1.261666536331177</v>
+        <v>1.258515477180481</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +1068,10 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>1.207499623298645</v>
+        <v>1.206664562225342</v>
       </c>
       <c r="D40" t="n">
-        <v>1.25840437412262</v>
+        <v>1.249807953834534</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +1084,10 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>1.551984786987305</v>
+        <v>1.546822309494019</v>
       </c>
       <c r="D41" t="n">
-        <v>1.444508075714111</v>
+        <v>1.443561434745789</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +1100,10 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>1.444979310035706</v>
+        <v>1.436720013618469</v>
       </c>
       <c r="D42" t="n">
-        <v>1.406959414482117</v>
+        <v>1.412424802780151</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +1116,10 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>1.342618823051453</v>
+        <v>1.340447306632996</v>
       </c>
       <c r="D43" t="n">
-        <v>1.343386292457581</v>
+        <v>1.340265512466431</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1132,10 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>1.344926357269287</v>
+        <v>1.360542893409729</v>
       </c>
       <c r="D44" t="n">
-        <v>1.333160281181335</v>
+        <v>1.349662184715271</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1148,10 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>2.062210559844971</v>
+        <v>2.041936635971069</v>
       </c>
       <c r="D45" t="n">
-        <v>1.741382479667664</v>
+        <v>1.729946255683899</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1164,10 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>1.417647838592529</v>
+        <v>1.415320038795471</v>
       </c>
       <c r="D46" t="n">
-        <v>1.39793586730957</v>
+        <v>1.370423555374146</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1180,10 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>1.68144166469574</v>
+        <v>1.676596879959106</v>
       </c>
       <c r="D47" t="n">
-        <v>1.531557679176331</v>
+        <v>1.529107451438904</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1196,10 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>1.75649619102478</v>
+        <v>1.749820709228516</v>
       </c>
       <c r="D48" t="n">
-        <v>1.596288919448853</v>
+        <v>1.57760226726532</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1212,10 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>1.850265264511108</v>
+        <v>1.84948718547821</v>
       </c>
       <c r="D49" t="n">
-        <v>1.637846350669861</v>
+        <v>1.62087881565094</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1228,10 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>1.437607169151306</v>
+        <v>1.434778332710266</v>
       </c>
       <c r="D50" t="n">
-        <v>1.405371904373169</v>
+        <v>1.398074150085449</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1244,10 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>1.555680394172668</v>
+        <v>1.54172956943512</v>
       </c>
       <c r="D51" t="n">
-        <v>1.455137848854065</v>
+        <v>1.447289109230042</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1260,10 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>1.574738502502441</v>
+        <v>1.573360204696655</v>
       </c>
       <c r="D52" t="n">
-        <v>1.455398917198181</v>
+        <v>1.450278282165527</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1276,10 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>1.43863046169281</v>
+        <v>1.439388275146484</v>
       </c>
       <c r="D53" t="n">
-        <v>1.401689648628235</v>
+        <v>1.40955114364624</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1292,10 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>1.419756174087524</v>
+        <v>1.423412203788757</v>
       </c>
       <c r="D54" t="n">
-        <v>1.386682152748108</v>
+        <v>1.401172161102295</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1308,10 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>1.051427006721497</v>
+        <v>1.074495077133179</v>
       </c>
       <c r="D55" t="n">
-        <v>1.182318687438965</v>
+        <v>1.178959131240845</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1324,10 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>1.675428986549377</v>
+        <v>1.673079967498779</v>
       </c>
       <c r="D56" t="n">
-        <v>1.53277599811554</v>
+        <v>1.522375583648682</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1340,10 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>1.558199286460876</v>
+        <v>1.565747022628784</v>
       </c>
       <c r="D57" t="n">
-        <v>1.469439148902893</v>
+        <v>1.44903564453125</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1356,10 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>1.449138879776001</v>
+        <v>1.44311535358429</v>
       </c>
       <c r="D58" t="n">
-        <v>1.415492415428162</v>
+        <v>1.400649666786194</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1372,10 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>2.468364238739014</v>
+        <v>2.46750020980835</v>
       </c>
       <c r="D59" t="n">
-        <v>1.983189702033997</v>
+        <v>1.966352939605713</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1388,10 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>1.549134850502014</v>
+        <v>1.552920699119568</v>
       </c>
       <c r="D60" t="n">
-        <v>1.443643689155579</v>
+        <v>1.458892345428467</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1404,10 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>1.281533241271973</v>
+        <v>1.280271053314209</v>
       </c>
       <c r="D61" t="n">
-        <v>1.300199747085571</v>
+        <v>1.299872636795044</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1420,10 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>1.123420000076294</v>
+        <v>1.129244565963745</v>
       </c>
       <c r="D62" t="n">
-        <v>1.243288993835449</v>
+        <v>1.228018879890442</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1436,10 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>1.33734405040741</v>
+        <v>1.358695864677429</v>
       </c>
       <c r="D63" t="n">
-        <v>1.328370213508606</v>
+        <v>1.366936564445496</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1452,10 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>1.117717504501343</v>
+        <v>1.120651364326477</v>
       </c>
       <c r="D64" t="n">
-        <v>1.2164067029953</v>
+        <v>1.210921406745911</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1468,10 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>1.766652464866638</v>
+        <v>1.769927740097046</v>
       </c>
       <c r="D65" t="n">
-        <v>1.59324586391449</v>
+        <v>1.595342636108398</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1484,10 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>1.564565539360046</v>
+        <v>1.571363091468811</v>
       </c>
       <c r="D66" t="n">
-        <v>1.449579477310181</v>
+        <v>1.470011472702026</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1500,10 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>1.051446795463562</v>
+        <v>1.064295053482056</v>
       </c>
       <c r="D67" t="n">
-        <v>1.19767439365387</v>
+        <v>1.189521312713623</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1516,10 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>1.289890766143799</v>
+        <v>1.274898290634155</v>
       </c>
       <c r="D68" t="n">
-        <v>1.309394478797913</v>
+        <v>1.29041576385498</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1532,10 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>1.223431825637817</v>
+        <v>1.213012099266052</v>
       </c>
       <c r="D69" t="n">
-        <v>1.267094135284424</v>
+        <v>1.263019919395447</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1548,10 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>1.288987755775452</v>
+        <v>1.289180755615234</v>
       </c>
       <c r="D70" t="n">
-        <v>1.304285526275635</v>
+        <v>1.293579697608948</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1564,10 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>1.215021848678589</v>
+        <v>1.213262796401978</v>
       </c>
       <c r="D71" t="n">
-        <v>1.270740866661072</v>
+        <v>1.266894936561584</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1580,10 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>1.138929486274719</v>
+        <v>1.135053157806396</v>
       </c>
       <c r="D72" t="n">
-        <v>1.239323973655701</v>
+        <v>1.233253359794617</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1596,10 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>1.717436552047729</v>
+        <v>1.716985106468201</v>
       </c>
       <c r="D73" t="n">
-        <v>1.554419279098511</v>
+        <v>1.557606220245361</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1612,10 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>1.43440854549408</v>
+        <v>1.43187403678894</v>
       </c>
       <c r="D74" t="n">
-        <v>1.393516063690186</v>
+        <v>1.390294671058655</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1628,10 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>1.331917881965637</v>
+        <v>1.342366337776184</v>
       </c>
       <c r="D75" t="n">
-        <v>1.329651236534119</v>
+        <v>1.326633930206299</v>
       </c>
     </row>
     <row r="76">
@@ -1644,10 +1644,10 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>1.520125508308411</v>
+        <v>1.519769430160522</v>
       </c>
       <c r="D76" t="n">
-        <v>1.430476665496826</v>
+        <v>1.446584224700928</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1660,10 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>1.661167144775391</v>
+        <v>1.666265368461609</v>
       </c>
       <c r="D77" t="n">
-        <v>1.536486983299255</v>
+        <v>1.540193319320679</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1676,10 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>1.452638626098633</v>
+        <v>1.472670197486877</v>
       </c>
       <c r="D78" t="n">
-        <v>1.415320158004761</v>
+        <v>1.423131704330444</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1692,10 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>2.570323944091797</v>
+        <v>2.583139657974243</v>
       </c>
       <c r="D79" t="n">
-        <v>2.017691850662231</v>
+        <v>2.013611793518066</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1708,10 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>1.424128174781799</v>
+        <v>1.423996806144714</v>
       </c>
       <c r="D80" t="n">
-        <v>1.394188404083252</v>
+        <v>1.381496548652649</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1724,10 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>1.657158374786377</v>
+        <v>1.66799259185791</v>
       </c>
       <c r="D81" t="n">
-        <v>1.533076286315918</v>
+        <v>1.525111675262451</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1740,10 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>1.927667737007141</v>
+        <v>1.936986327171326</v>
       </c>
       <c r="D82" t="n">
-        <v>1.663143634796143</v>
+        <v>1.669294357299805</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1756,10 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>1.318983793258667</v>
+        <v>1.323512673377991</v>
       </c>
       <c r="D83" t="n">
-        <v>1.320770978927612</v>
+        <v>1.315356254577637</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1772,10 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>1.415760040283203</v>
+        <v>1.43441641330719</v>
       </c>
       <c r="D84" t="n">
-        <v>1.377146363258362</v>
+        <v>1.404361009597778</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1788,10 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>1.277809023857117</v>
+        <v>1.276313781738281</v>
       </c>
       <c r="D85" t="n">
-        <v>1.305254340171814</v>
+        <v>1.304611563682556</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1804,10 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>1.071721196174622</v>
+        <v>1.074371457099915</v>
       </c>
       <c r="D86" t="n">
-        <v>1.185998797416687</v>
+        <v>1.180667161941528</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_afr_2025.xlsx
+++ b/notebooks/XGBoost/predictions_afr_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>predictions</t>
+          <t>СКР_прогноз</t>
         </is>
       </c>
     </row>
@@ -460,10 +455,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>1.333839774131775</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.332483649253845</v>
+        <v>1.320698380470276</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +468,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>1.502897381782532</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.431456446647644</v>
+        <v>1.519048571586609</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +481,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>1.504938244819641</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.413058638572693</v>
+        <v>1.438102960586548</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +494,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>1.655352473258972</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.527954816818237</v>
+        <v>1.650223970413208</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +507,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>1.140672922134399</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.246144413948059</v>
+        <v>1.091194033622742</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +520,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>1.208008527755737</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.258081793785095</v>
+        <v>1.195487022399902</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +533,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>1.142362356185913</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.237136721611023</v>
+        <v>1.103552937507629</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +546,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>1.149627685546875</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.249036908149719</v>
+        <v>1.125068545341492</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +559,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>1.415530920028687</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.374614477157593</v>
+        <v>1.410733819007874</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>1.220258593559265</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.266632318496704</v>
+        <v>1.219992756843567</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +585,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>1.605180501937866</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.501436829566956</v>
+        <v>1.591449737548828</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +598,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>1.61126708984375</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.498475432395935</v>
+        <v>1.574221849441528</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +611,7 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>1.369040369987488</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.368060946464539</v>
+        <v>1.401193261146545</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +624,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>1.686344385147095</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.533150196075439</v>
+        <v>1.663706660270691</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>1.539897441864014</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.439299583435059</v>
+        <v>1.559272646903992</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>1.222097277641296</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.273413062095642</v>
+        <v>1.134391069412231</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +663,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>1.342038869857788</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.323188185691833</v>
+        <v>1.340337991714478</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +676,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>1.660814642906189</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.530423879623413</v>
+        <v>1.662165760993958</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +689,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>1.337565064430237</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.329493880271912</v>
+        <v>1.369214534759521</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +702,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>1.259890913963318</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.253034830093384</v>
+        <v>1.224265575408936</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +715,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>1.501935958862305</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.418921709060669</v>
+        <v>1.502238631248474</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +728,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>1.568055868148804</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.460103869438171</v>
+        <v>1.57658839225769</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>1.537211894989014</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.411762595176697</v>
+        <v>1.532557487487793</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>1.432950973510742</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.417754173278809</v>
+        <v>1.425227403640747</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +767,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>1.690935492515564</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.516912341117859</v>
+        <v>1.666736841201782</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>1.297560811042786</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.303098559379578</v>
+        <v>1.221354246139526</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>1.02957284450531</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.101929783821106</v>
+        <v>1.030835747718811</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +806,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>1.200989484786987</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.245800375938416</v>
+        <v>1.263343095779419</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +819,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>1.414622187614441</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.392966151237488</v>
+        <v>1.387645125389099</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +832,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>1.321791768074036</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1.341306686401367</v>
+        <v>1.377963542938232</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +845,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>1.457277655601501</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.425849080085754</v>
+        <v>1.454156756401062</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>1.895996451377869</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1.639363288879395</v>
+        <v>1.939980983734131</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +871,7 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>1.302320599555969</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1.323935151100159</v>
+        <v>1.345413208007812</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>1.334379911422729</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1.341401100158691</v>
+        <v>1.283907175064087</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +897,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>1.506269812583923</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.43855094909668</v>
+        <v>1.518867015838623</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +910,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>1.527469396591187</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1.430280804634094</v>
+        <v>1.53916335105896</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +923,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>1.507794976234436</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.412416815757751</v>
+        <v>1.512329697608948</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +936,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>1.206899523735046</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.258515477180481</v>
+        <v>1.151605129241943</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +949,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>1.206664562225342</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.249807953834534</v>
+        <v>1.200635433197021</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +962,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>1.546822309494019</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.443561434745789</v>
+        <v>1.549884915351868</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +975,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>1.436720013618469</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.412424802780151</v>
+        <v>1.434096932411194</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +988,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>1.340447306632996</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.340265512466431</v>
+        <v>1.305859088897705</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1001,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>1.360542893409729</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.349662184715271</v>
+        <v>1.369371175765991</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1014,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>2.041936635971069</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.729946255683899</v>
+        <v>2.030985832214355</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1027,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>1.415320038795471</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.370423555374146</v>
+        <v>1.413841724395752</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1040,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>1.676596879959106</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1.529107451438904</v>
+        <v>1.620574593544006</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>1.749820709228516</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1.57760226726532</v>
+        <v>1.752201318740845</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1066,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>1.84948718547821</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.62087881565094</v>
+        <v>1.794204950332642</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>1.434778332710266</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.398074150085449</v>
+        <v>1.440751910209656</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1092,7 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>1.54172956943512</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1.447289109230042</v>
+        <v>1.568302392959595</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1105,7 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>1.573360204696655</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1.450278282165527</v>
+        <v>1.585259437561035</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1118,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>1.439388275146484</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.40955114364624</v>
+        <v>1.422487258911133</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1131,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>1.423412203788757</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.401172161102295</v>
+        <v>1.402877569198608</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1144,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>1.074495077133179</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.178959131240845</v>
+        <v>1.074373483657837</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1157,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>1.673079967498779</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1.522375583648682</v>
+        <v>1.612966895103455</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>1.565747022628784</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.44903564453125</v>
+        <v>1.549330472946167</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>1.44311535358429</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1.400649666786194</v>
+        <v>1.428108930587769</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1196,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>2.46750020980835</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1.966352939605713</v>
+        <v>2.479401350021362</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1209,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>1.552920699119568</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.458892345428467</v>
+        <v>1.539429783821106</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1222,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>1.280271053314209</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1.299872636795044</v>
+        <v>1.266716599464417</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1235,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>1.129244565963745</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.228018879890442</v>
+        <v>1.092652440071106</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1248,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>1.358695864677429</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.366936564445496</v>
+        <v>1.324142575263977</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1261,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>1.120651364326477</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.210921406745911</v>
+        <v>1.106462121009827</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>1.769927740097046</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.595342636108398</v>
+        <v>1.734674572944641</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1287,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>1.571363091468811</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.470011472702026</v>
+        <v>1.572079181671143</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1300,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>1.064295053482056</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.189521312713623</v>
+        <v>1.066775918006897</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1313,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>1.274898290634155</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.29041576385498</v>
+        <v>1.282639026641846</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>1.213012099266052</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.263019919395447</v>
+        <v>1.248791098594666</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1339,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>1.289180755615234</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1.293579697608948</v>
+        <v>1.284099221229553</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1352,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>1.213262796401978</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1.266894936561584</v>
+        <v>1.187752485275269</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>1.135053157806396</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1.233253359794617</v>
+        <v>1.136688232421875</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1378,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>1.716985106468201</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1.557606220245361</v>
+        <v>1.716901540756226</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1391,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>1.43187403678894</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1.390294671058655</v>
+        <v>1.415062189102173</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>1.342366337776184</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1.326633930206299</v>
+        <v>1.32257354259491</v>
       </c>
     </row>
     <row r="76">
@@ -1644,10 +1417,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>1.519769430160522</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1.446584224700928</v>
+        <v>1.445321321487427</v>
       </c>
     </row>
     <row r="77">
@@ -1660,10 +1430,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>1.666265368461609</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1.540193319320679</v>
+        <v>1.668561339378357</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1443,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>1.472670197486877</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1.423131704330444</v>
+        <v>1.435551404953003</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1456,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>2.583139657974243</v>
-      </c>
-      <c r="D79" t="n">
-        <v>2.013611793518066</v>
+        <v>2.405396699905396</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1469,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>1.423996806144714</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1.381496548652649</v>
+        <v>1.414645791053772</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>1.66799259185791</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1.525111675262451</v>
+        <v>1.660044312477112</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>1.936986327171326</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1.669294357299805</v>
+        <v>1.946242094039917</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1508,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>1.323512673377991</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1.315356254577637</v>
+        <v>1.324826121330261</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1521,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>1.43441641330719</v>
-      </c>
-      <c r="D84" t="n">
-        <v>1.404361009597778</v>
+        <v>1.420466542243958</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1534,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>1.276313781738281</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1.304611563682556</v>
+        <v>1.268610000610352</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>1.074371457099915</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1.180667161941528</v>
+        <v>1.077500939369202</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_afr_2025.xlsx
+++ b/notebooks/XGBoost/predictions_afr_2025.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
     </row>
@@ -455,7 +455,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>1.320698380470276</v>
+        <v>1.336864948272705</v>
       </c>
     </row>
     <row r="3">
@@ -468,7 +468,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>1.519048571586609</v>
+        <v>1.508382558822632</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>1.438102960586548</v>
+        <v>1.433699607849121</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>1.650223970413208</v>
+        <v>1.662878632545471</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>1.091194033622742</v>
+        <v>1.088302969932556</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>1.195487022399902</v>
+        <v>1.168341040611267</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>1.103552937507629</v>
+        <v>1.10222327709198</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>1.125068545341492</v>
+        <v>1.101931810379028</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>1.410733819007874</v>
+        <v>1.389797449111938</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>1.219992756843567</v>
+        <v>1.213855266571045</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>1.591449737548828</v>
+        <v>1.594377875328064</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>1.574221849441528</v>
+        <v>1.590054273605347</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>1.401193261146545</v>
+        <v>1.373598217964172</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>1.663706660270691</v>
+        <v>1.672683954238892</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>1.559272646903992</v>
+        <v>1.566665649414062</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>1.134391069412231</v>
+        <v>1.155155420303345</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>1.340337991714478</v>
+        <v>1.335546374320984</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>1.662165760993958</v>
+        <v>1.656781315803528</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>1.369214534759521</v>
+        <v>1.338416337966919</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>1.224265575408936</v>
+        <v>1.213730335235596</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +715,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>1.502238631248474</v>
+        <v>1.505309224128723</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>1.57658839225769</v>
+        <v>1.57332718372345</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>1.532557487487793</v>
+        <v>1.53912091255188</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>1.425227403640747</v>
+        <v>1.425539374351501</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>1.666736841201782</v>
+        <v>1.667881965637207</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>1.221354246139526</v>
+        <v>1.240600824356079</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>1.030835747718811</v>
+        <v>1.030391335487366</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>1.263343095779419</v>
+        <v>1.24263322353363</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>1.387645125389099</v>
+        <v>1.389645457267761</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>1.377963542938232</v>
+        <v>1.351218819618225</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>1.454156756401062</v>
+        <v>1.454728960990906</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>1.939980983734131</v>
+        <v>1.941800355911255</v>
       </c>
     </row>
     <row r="34">
@@ -871,7 +871,7 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>1.345413208007812</v>
+        <v>1.291747212409973</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>1.283907175064087</v>
+        <v>1.27643871307373</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>1.518867015838623</v>
+        <v>1.509303092956543</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>1.53916335105896</v>
+        <v>1.532689452171326</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>1.512329697608948</v>
+        <v>1.513030052185059</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>1.151605129241943</v>
+        <v>1.151728510856628</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>1.200635433197021</v>
+        <v>1.196346521377563</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>1.549884915351868</v>
+        <v>1.553197622299194</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>1.434096932411194</v>
+        <v>1.437572598457336</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>1.305859088897705</v>
+        <v>1.323032140731812</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>1.369371175765991</v>
+        <v>1.335645318031311</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>2.030985832214355</v>
+        <v>2.037793397903442</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1027,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>1.413841724395752</v>
+        <v>1.418779134750366</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>1.620574593544006</v>
+        <v>1.611404418945312</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>1.752201318740845</v>
+        <v>1.763492226600647</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>1.794204950332642</v>
+        <v>1.790067076683044</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>1.440751910209656</v>
+        <v>1.434693336486816</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>1.568302392959595</v>
+        <v>1.566303849220276</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>1.585259437561035</v>
+        <v>1.564945578575134</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>1.422487258911133</v>
+        <v>1.425087332725525</v>
       </c>
     </row>
     <row r="54">
@@ -1131,7 +1131,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>1.402877569198608</v>
+        <v>1.39903998374939</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>1.074373483657837</v>
+        <v>1.073309540748596</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1157,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>1.612966895103455</v>
+        <v>1.63327431678772</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>1.549330472946167</v>
+        <v>1.546802043914795</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>1.428108930587769</v>
+        <v>1.424760818481445</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>2.479401350021362</v>
+        <v>2.456251621246338</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>1.539429783821106</v>
+        <v>1.556383609771729</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>1.266716599464417</v>
+        <v>1.274481654167175</v>
       </c>
     </row>
     <row r="62">
@@ -1235,7 +1235,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>1.092652440071106</v>
+        <v>1.096027612686157</v>
       </c>
     </row>
     <row r="63">
@@ -1248,7 +1248,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>1.324142575263977</v>
+        <v>1.342745780944824</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>1.106462121009827</v>
+        <v>1.105615139007568</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>1.734674572944641</v>
+        <v>1.728121757507324</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>1.572079181671143</v>
+        <v>1.56807279586792</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>1.066775918006897</v>
+        <v>1.067682027816772</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>1.282639026641846</v>
+        <v>1.290479898452759</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>1.248791098594666</v>
+        <v>1.202763676643372</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>1.284099221229553</v>
+        <v>1.293352365493774</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>1.187752485275269</v>
+        <v>1.182982921600342</v>
       </c>
     </row>
     <row r="72">
@@ -1365,7 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>1.136688232421875</v>
+        <v>1.115312695503235</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>1.716901540756226</v>
+        <v>1.711973786354065</v>
       </c>
     </row>
     <row r="74">
@@ -1391,7 +1391,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>1.415062189102173</v>
+        <v>1.417373895645142</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>1.32257354259491</v>
+        <v>1.323015809059143</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>1.445321321487427</v>
+        <v>1.451780438423157</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>1.668561339378357</v>
+        <v>1.6659095287323</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>1.435551404953003</v>
+        <v>1.444075226783752</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>2.405396699905396</v>
+        <v>2.542999982833862</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>1.414645791053772</v>
+        <v>1.418138384819031</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>1.660044312477112</v>
+        <v>1.66261875629425</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>1.946242094039917</v>
+        <v>1.939199924468994</v>
       </c>
     </row>
     <row r="83">
@@ -1508,7 +1508,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>1.324826121330261</v>
+        <v>1.297478437423706</v>
       </c>
     </row>
     <row r="84">
@@ -1521,7 +1521,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>1.420466542243958</v>
+        <v>1.436186552047729</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>1.268610000610352</v>
+        <v>1.268443822860718</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>1.077500939369202</v>
+        <v>1.076826095581055</v>
       </c>
     </row>
   </sheetData>
